--- a/AAII_Financials/Quarterly/LOW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LOW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="92">
   <si>
     <t>LOW</t>
   </si>
@@ -656,517 +656,529 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
         <v>46143</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46052</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45870</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45779</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45597</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45506</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45415</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45324</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45233</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45142</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45051</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44960</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44862</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44771</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44680</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44589</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44498</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44407</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44316</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44225</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44134</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44043</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43952</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43861</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43770</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43679</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43588</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43497</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43406</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43315</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43224</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43133</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43042</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42951</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42860</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42769</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25956000</v>
+      </c>
+      <c r="E8" s="3">
         <v>23078000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20585000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20813000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>23959000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>20930000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>18554000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20170000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>23586000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21364000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18602000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20471000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>24956000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>22347000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>22445000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>23479000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>27476000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>23659000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>21339000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>22918000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>27570000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>24422000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>20311000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>22309000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>27302000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>19675000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>16027000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>17388000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>20992000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>17741000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>15647000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>17415000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>20888000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>17360000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>15494000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>16770000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>19495000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>16860000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>15784000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>15739000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>17459000</v>
+      </c>
+      <c r="E9" s="3">
         <v>15535000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13904000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13697000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15858000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13944000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12457000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13374000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15691000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14274000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12575000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13580000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16557000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>14820000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15188000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>15661000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>18343000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>15609000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14312000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>15331000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>18258000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>16292000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>13855000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>15009000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>17998000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>13162000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>11046000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>11748000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>14252000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>12160000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>11610000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>12038000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>14003000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>11612000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>10268000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>11057000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>12825000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>11060000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>10352000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>10332000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8497000</v>
+      </c>
+      <c r="E10" s="3">
         <v>7543000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6681000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7116000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8101000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6986000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6097000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6796000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7895000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7090000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6027000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6891000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8399000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>7527000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>7257000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>7818000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9133000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8050000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>7027000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>7587000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9312000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8130000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6456000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>7300000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>9304000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>6513000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4981000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5640000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>6740000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5581000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4037000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>5377000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>6885000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>5748000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>5226000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>5713000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>6670000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>5800000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>5432000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>5407000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1209,8 +1221,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1331,8 +1344,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1453,55 +1469,58 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>53000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>-92000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>54000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>43000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>102000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1509,54 +1528,54 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>29000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>47000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>27000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>59000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>203000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1361000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>438000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>9000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-1111000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>53000</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
         <v>623000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>275000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>230000</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
         <v>0</v>
       </c>
@@ -1567,138 +1586,144 @@
         <v>0</v>
       </c>
       <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3">
         <v>464000</v>
       </c>
-      <c r="AO14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AP14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>572000</v>
+      </c>
+      <c r="E15" s="3">
         <v>566000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>563000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>475000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>457000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>446000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>445000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>433000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>423000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>428000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>442000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>434000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>427000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>415000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>421000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>451000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>449000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>445000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>436000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>425000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>409000</v>
-      </c>
-      <c r="X15" s="3">
-        <v>391000</v>
       </c>
       <c r="Y15" s="3">
         <v>391000</v>
       </c>
       <c r="Z15" s="3">
+        <v>391000</v>
+      </c>
+      <c r="AA15" s="3">
         <v>355000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>327000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>326000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>338000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>310000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>311000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>302000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>339000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>423000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>336000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>349000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>367000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>358000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>357000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>365000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>388000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>378000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1738,252 +1763,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22487000</v>
+      </c>
+      <c r="E17" s="3">
         <v>20524000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18824000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18332000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>20490000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>18436000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16816000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17580000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>20096000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18711000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16914000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17775000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>21070000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18957000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20741000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>22555000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23247000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>20357000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>19490000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>20129000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>23360000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>21177000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>18787000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>21194000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>23345000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>17684000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>15069000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>15830000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>18611000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>16324000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>16215000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>16458000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>18725000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>15895000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>14396000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>15223000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>17113000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>15765000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>14515000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>14800000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3469000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2554000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1761000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2481000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3469000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2494000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1738000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2590000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3490000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2653000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1688000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2696000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3886000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3390000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1704000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>924000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4229000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3302000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1849000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2789000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4210000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3245000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1524000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1115000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3957000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1991000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>958000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1558000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2381000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1417000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-568000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>957000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2163000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1465000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1098000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1547000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2382000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1095000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1269000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>939000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2026,8 +2058,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2070,574 +2103,589 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>12000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>10000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-6000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-14000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5000</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-3000</v>
       </c>
       <c r="X20" s="3">
         <v>-3000</v>
       </c>
       <c r="Y20" s="3">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>1000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2000</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>11000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1000</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>7000</v>
       </c>
       <c r="AI20" s="3">
         <v>7000</v>
       </c>
       <c r="AJ20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>4000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-2000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>1000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4041000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3120000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2324000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2956000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3926000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2940000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2183000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3023000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3913000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3081000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2130000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3130000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4313000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3805000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2188000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1436000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4732000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3799000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2329000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3265000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4671000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3685000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1966000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1521000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4333000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2364000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1335000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1904000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2739000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1753000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-166000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1419000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2534000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1851000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1494000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1925000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2762000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1481000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1668000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1351000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>392000</v>
+      </c>
+      <c r="E22" s="3">
         <v>408000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>417000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>393000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>355000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>362000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>363000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>367000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>369000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>373000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>372000</v>
       </c>
       <c r="N22" s="3">
         <v>372000</v>
       </c>
       <c r="O22" s="3">
+        <v>372000</v>
+      </c>
+      <c r="P22" s="3">
         <v>376000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>365000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>333000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>305000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>263000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>237000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>221000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>218000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>213000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>208000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>204000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>222000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>221000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>205000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>179000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>178000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>180000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>161000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>158000</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>160000</v>
       </c>
       <c r="AI22" s="3">
         <v>160000</v>
       </c>
       <c r="AJ22" s="3">
+        <v>160000</v>
+      </c>
+      <c r="AK22" s="3">
         <v>159000</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>158000</v>
       </c>
       <c r="AL22" s="3">
         <v>158000</v>
       </c>
       <c r="AM22" s="3">
+        <v>158000</v>
+      </c>
+      <c r="AN22" s="3">
         <v>160000</v>
-      </c>
-      <c r="AN22" s="3">
-        <v>158000</v>
       </c>
       <c r="AO22" s="3">
         <v>158000</v>
       </c>
       <c r="AP22" s="3">
+        <v>158000</v>
+      </c>
+      <c r="AQ22" s="3">
         <v>163000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3175000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2155000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1304000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2129000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3156000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2157000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1502000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2219000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3130000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2301000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1339000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2351000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3545000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2939000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1383000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>629000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3965000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3059000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1614000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2566000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3994000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3034000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1320000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>894000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3738000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1786000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>775000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1381000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2212000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1255000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-725000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>804000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2010000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1305000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>944000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1387000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2223000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>934000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1110000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>776000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>776000</v>
+      </c>
+      <c r="E24" s="3">
         <v>527000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>304000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>513000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>758000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>516000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>378000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>524000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>747000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>546000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>319000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>578000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>872000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>679000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>425000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>475000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>973000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>726000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>407000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>670000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>976000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>713000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>342000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>202000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>910000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>449000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>265000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>332000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>536000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>209000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>97000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>175000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>490000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>317000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>370000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>515000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>804000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>332000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>447000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>397000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2758,252 +2806,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2399000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1628000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1000000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1616000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2398000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1641000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1124000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1695000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2383000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1755000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1020000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1773000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2673000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2260000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>958000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>154000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2992000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2333000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1207000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1896000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3018000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2321000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>978000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>692000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2828000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1337000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>510000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1049000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1676000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1046000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-822000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>629000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1520000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>988000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>574000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>872000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1419000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>602000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>663000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>379000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2392000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1623000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>997000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1612000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2391000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1636000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1122000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1691000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2377000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1750000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1018000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1769000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2666000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2254000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>954000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>152000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2983000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2325000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1202000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1889000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3007000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2312000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>974000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>689000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2816000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1333000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>508000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1046000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1670000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1043000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-819000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>628000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1515000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>985000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>573000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>870000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1413000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>600000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>643000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>376000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3124,8 +3181,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3195,8 +3255,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -3216,24 +3276,24 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-20000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3246,8 +3306,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3368,8 +3431,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3490,8 +3556,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3534,208 +3603,214 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>-12000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-10000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>6000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>14000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5000</v>
-      </c>
-      <c r="W32" s="3">
-        <v>3000</v>
       </c>
       <c r="X32" s="3">
         <v>3000</v>
       </c>
       <c r="Y32" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>4000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>-7000</v>
       </c>
       <c r="AI32" s="3">
         <v>-7000</v>
       </c>
       <c r="AJ32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="AK32" s="3">
         <v>1000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>2000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>3000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>1000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2399000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1628000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1000000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1616000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2398000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1641000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1124000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1695000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2383000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1755000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1020000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1773000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2673000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2260000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>954000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>152000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2983000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2325000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1202000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1889000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3007000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2312000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>974000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>689000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2816000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1333000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>508000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1046000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1670000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1043000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-821000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>628000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1515000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>985000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>553000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>870000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1413000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>600000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>643000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>376000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3856,257 +3931,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2399000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1628000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1000000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1616000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2398000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1641000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1124000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1695000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2383000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1755000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1020000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1773000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2673000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2260000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>954000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>152000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2983000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2325000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1202000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1889000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3007000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2312000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>974000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>689000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2816000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1333000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>508000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1046000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1670000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1043000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-821000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>628000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1515000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>985000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>553000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>870000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1413000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>600000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>643000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>376000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
         <v>46143</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46052</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45870</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45779</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45597</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45506</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45415</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45324</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45233</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45142</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45051</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44960</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44862</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44771</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44680</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44589</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44498</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44407</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44316</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44225</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44134</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44043</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43952</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43861</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43770</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43679</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43588</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43497</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43406</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43315</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43224</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43133</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43042</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42951</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42860</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42769</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4149,8 +4233,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4193,130 +4278,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3172000</v>
+      </c>
+      <c r="E41" s="3">
         <v>786000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>982000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>621000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4860000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3054000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1761000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3271000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4360000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3237000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>921000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1210000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3494000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2950000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1348000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3192000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1482000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3414000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1133000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6121000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4835000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6692000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4690000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8249000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>11641000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5955000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>716000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>794000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1796000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2973000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>511000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1668000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2251000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1565000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>588000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>743000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1696000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1963000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>558000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>960000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4330,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>396000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -4351,17 +4440,17 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>321000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>374000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>423000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4374,27 +4463,27 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W42" s="3">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X42" s="3">
         <v>900000</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="Z42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA42" s="3">
         <v>1450000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1085000</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>8</v>
       </c>
@@ -4410,59 +4499,62 @@
       <c r="AG42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AH42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI42" s="3">
         <v>27000</v>
-      </c>
-      <c r="AI42" s="3">
-        <v>17000</v>
       </c>
       <c r="AJ42" s="3">
         <v>17000</v>
       </c>
       <c r="AK42" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AL42" s="3">
         <v>16000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>15000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>13000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>14000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>19000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1238000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1151000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1090000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1216000</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3">
         <v>94000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4481,8 +4573,8 @@
       <c r="P43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4559,374 +4651,386 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>17737000</v>
+      </c>
+      <c r="E44" s="3">
         <v>18447000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>17300000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>17183000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>16342000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>18335000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>17409000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>17566000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>16841000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>18224000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>16894000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>17530000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>17422000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>19522000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>18532000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>19817000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>19329000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>20239000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>17605000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>16685000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>17322000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>18382000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>16193000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>15712000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>13831000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>14283000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>13179000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>13716000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>13730000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>15026000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>12561000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>12365000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>11885000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>13204000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>11393000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>12393000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>11407000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>12254000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>10458000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>10990000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1195000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1778000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1583000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1200000</v>
       </c>
-      <c r="G45" s="3">
-        <v>1041000</v>
-      </c>
       <c r="H45" s="3">
+        <v>1437000</v>
+      </c>
+      <c r="I45" s="3">
         <v>1286000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1094000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1140000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1136000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1289000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1256000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>907000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>946000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1023000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1562000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1982000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1856000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1958000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1322000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2043000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2026000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1742000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1443000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1505000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1160000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1688000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1423000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1152000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1270000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1336000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1156000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1078000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1330000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1247000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>775000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>858000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>917000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1045000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>965000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>708000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23342000</v>
+      </c>
+      <c r="E46" s="3">
         <v>22162000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>20955000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>20220000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22639000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22675000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>20358000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21977000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22337000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>22750000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>19071000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>19968000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>22236000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>23918000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>21442000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>24991000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>22667000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>25611000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>20060000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>24849000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>25083000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>26816000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>22326000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>26916000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>27717000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>21926000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>15318000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>15662000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>16796000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>19335000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>14228000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>15138000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>15483000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>16033000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>12772000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>14009000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>14033000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>15276000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>12000000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>12728000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4969,12 +5073,12 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
         <v>21000</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4990,8 +5094,8 @@
       <c r="W47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -5017,184 +5121,190 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH47" s="3">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI47" s="3">
         <v>290000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>87000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>321000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>27000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>38000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>10000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>137000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>12000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>88000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22347000</v>
+      </c>
+      <c r="E48" s="3">
         <v>22436000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22665000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22654000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21595000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21435000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21387000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21357000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21334000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21360000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21386000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21174000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21023000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20906000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21085000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20787000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>22871000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>23021000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>23179000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>23086000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>22851000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>22945000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>22987000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>22506000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>22410000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>22377000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>22560000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>22244000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>22170000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>22076000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>18432000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>18923000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>19172000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>19500000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>19721000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>19818000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>19762000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>19748000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>19949000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>20037000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9666000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9752000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9853000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9976000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1667000</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>588000</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
@@ -5219,38 +5329,38 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>8</v>
+      <c r="S49" s="3">
+        <v>0</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U49" s="3">
+      <c r="U49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V49" s="3">
         <v>833000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>846000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>853000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>864000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>311000</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC49" s="3">
-        <v>303000</v>
+      <c r="AC49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD49" s="3">
         <v>303000</v>
@@ -5265,34 +5375,37 @@
         <v>303000</v>
       </c>
       <c r="AH49" s="3">
+        <v>303000</v>
+      </c>
+      <c r="AI49" s="3">
         <v>1272000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1271000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1288000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1307000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1327000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1255000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1081000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1082000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>1034000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5413,8 +5526,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5535,130 +5651,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>526000</v>
+      </c>
+      <c r="E52" s="3">
         <v>591000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>671000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>603000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>573000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1144000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>525000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1148000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1079000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1140000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1090000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1097000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1032000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>943000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1160000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1195000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1187000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1093000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>568000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>619000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>617000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>575000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1111000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1458000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1636000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1529000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1290000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1555000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1426000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1505000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1545000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1090000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1092000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1095000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1464000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1591000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1608000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1371000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1365000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1483000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5779,130 +5901,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>55881000</v>
+      </c>
+      <c r="E54" s="3">
         <v>54941000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>54144000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>53453000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>46614000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>45372000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>43102000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>44743000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>44934000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>45365000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>41795000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>42519000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>44521000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>45917000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>43708000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>46973000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>46725000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>49725000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>44640000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>49400000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>49404000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>51200000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>46735000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>50880000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>51763000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>45832000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>39471000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>39764000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>40695000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>43219000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>34508000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>36713000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>37105000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>38237000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>35291000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>36783000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>36668000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>37613000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>34408000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>35370000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5945,8 +6073,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5989,740 +6118,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11076000</v>
+      </c>
+      <c r="E57" s="3">
         <v>11975000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9762000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10236000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9513000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11235000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9290000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10602000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10336000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11737000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8704000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9914000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10333000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11885000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10524000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12249000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12631000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>13831000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11354000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11334000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12011000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>13964000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10884000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12759000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12916000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10841000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>7659000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>8822000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9499000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>11485000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>8279000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9283000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>8984000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>10104000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>6590000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>8903000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>8649000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>9905000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>6651000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>7836000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3093000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1868000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3144000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3128000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4717000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4751000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3149000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3084000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1842000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1846000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1024000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1077000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1126000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1186000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1084000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>609000</v>
-      </c>
-      <c r="S58" s="3">
-        <v>121000</v>
       </c>
       <c r="T58" s="3">
         <v>121000</v>
       </c>
       <c r="U58" s="3">
+        <v>121000</v>
+      </c>
+      <c r="V58" s="3">
         <v>868000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2352000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2344000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1338000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1112000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>609000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1609000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1604000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2538000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1211000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1009000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1008000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1832000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1117000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>894000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>896000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1431000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>468000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>296000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>295000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1305000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>800000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5795000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5459000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3963000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5064000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6294000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5549000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4096000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4933000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5013000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5053000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3705000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4755000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5127000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5373000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7903000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8018000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7614000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7879000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7446000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7148000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7309000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7590000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6734000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6196000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6845000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5880000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4985000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5030000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5327000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>5288000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4386000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4669000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4703000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4774000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4075000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>4367000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>4680000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>4486000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>4018000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>3997000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>21132000</v>
+      </c>
+      <c r="E60" s="3">
         <v>20274000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19463000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19451000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>21622000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>22388000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18757000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19447000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18246000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>19506000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15568000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>16496000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17612000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>19210000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>19511000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>20876000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>20366000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>21831000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>19668000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>20834000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>21664000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>22892000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>18730000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>19564000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>21370000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>18325000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>15182000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>15063000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>15835000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>17781000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>14497000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>15069000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>14581000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>15774000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>12096000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>13738000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>13625000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>14686000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>11974000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>12633000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>38938000</v>
+      </c>
+      <c r="E61" s="3">
         <v>40688000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>41533000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>41593000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>34373000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>34243000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>36564000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>36693000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>38454000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>38462000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>39197000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>39068000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>39542000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>39411000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>32876000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>32904000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>28763000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>28776000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>23859000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>23881000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>21967000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>21906000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>20668000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>21185000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>20197000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>20200000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>16768000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>16635000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>16538000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>16542000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>14391000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>14460000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>14937000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>14948000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>15564000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>15570000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>15788000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>15770000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>14394000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>14395000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>794000</v>
+      </c>
+      <c r="E62" s="3">
         <v>762000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>764000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>710000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>736000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>729000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>744000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>762000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>741000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>778000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>855000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>874000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>868000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>800000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5575000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6061000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6038000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5995000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5929000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6261000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5948000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5957000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5900000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6058000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>5840000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>5591000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5549000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5608000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5682000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5660000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1976000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1790000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1806000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1770000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1758000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1733000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1719000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1626000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1606000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1634000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6843,8 +6991,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6965,8 +7116,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7087,130 +7241,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>63318000</v>
+      </c>
+      <c r="E66" s="3">
         <v>64211000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>64061000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>63835000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>58014000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>58626000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>57333000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>58162000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>58697000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>59971000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>56845000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>57666000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>59253000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>60627000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>57962000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>59841000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>55167000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>56602000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>49456000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>50976000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>49579000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>50755000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>45298000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>46807000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>47407000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>44116000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>37499000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>37306000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>38055000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>39983000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>30864000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>31319000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>31324000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>32492000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>29418000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>31041000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>31132000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>32082000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>27974000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>28771000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7253,8 +7413,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7375,8 +7536,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7497,8 +7661,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7619,8 +7786,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7741,130 +7911,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8187000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-9884000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10839000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-11165000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-12108000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-13833000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-14799000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-13993000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-14342000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-15188000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-15637000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-15744000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-15341000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-15310000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-14862000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-13313000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-8895000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-7367000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5115000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1913000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-460000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>98000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1117000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3942000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4134000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1722000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1727000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2238000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2439000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>3095000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>3452000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5156000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5517000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5405000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5425000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>5289000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>5253000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>5346000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>6241000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>6376000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7985,8 +8161,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8107,8 +8286,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8229,130 +8411,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-7437000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-9270000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-9917000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-10382000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-11400000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-13254000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-14231000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-13419000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-13763000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-14606000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-15050000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-15147000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-14732000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-14710000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-14254000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-12868000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-8442000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-6877000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-4816000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-1576000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-175000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>445000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1437000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4073000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4356000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1716000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1972000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2458000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2640000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3236000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3644000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5394000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5781000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5745000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5873000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>5742000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>5536000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>5531000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>6434000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>6599000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8473,257 +8661,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
         <v>46143</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46052</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45870</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45779</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45597</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45506</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45415</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45324</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45233</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45142</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45051</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44960</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44862</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44771</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44680</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44589</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44498</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44407</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44316</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44225</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44134</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44043</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43952</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43861</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43770</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43679</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43588</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43497</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43406</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43315</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43224</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43133</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43042</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42951</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42860</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42769</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2399000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1628000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1000000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1616000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2398000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1641000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1124000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1695000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2383000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1755000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1020000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1773000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2673000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2260000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>954000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>152000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2983000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2325000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1202000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1889000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3007000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2312000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>974000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>689000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2816000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1333000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>508000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1046000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1670000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1043000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-821000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>628000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1515000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>985000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>553000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>870000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1413000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>600000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>643000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>376000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8766,130 +8963,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>503000</v>
+      </c>
+      <c r="E83" s="3">
         <v>504000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>498000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>494000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>481000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>486000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>496000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>486000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>476000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>465000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>472000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>502000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>504000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>503000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>472000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>502000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>504000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>503000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>494000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>481000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>464000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>443000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>442000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>405000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>374000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>373000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>381000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>345000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>347000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>337000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>401000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>455000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>364000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>387000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>392000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>380000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>379000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>389000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>400000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>412000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9010,8 +9211,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9132,8 +9336,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9254,8 +9461,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9376,8 +9586,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9498,130 +9711,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3659000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3350000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1567000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>687000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4231000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3379000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>911000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1299000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3153000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4262000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1108000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1064000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3862000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2106000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>451000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2126000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3035000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2977000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>934000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2266000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2421000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4492000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-436000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-267000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>7302000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4450000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>185000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>528000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1446000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2149000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-605000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1011000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2358000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>3429000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-307000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>298000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1779000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>3295000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>348000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>641000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9664,130 +9883,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-542000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-521000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-603000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-597000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-495000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-518000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-548000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-571000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-426000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-382000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-620000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-579000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-385000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-380000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-739000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-403000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-344000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-343000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-597000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-410000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-385000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-461000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-619000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-462000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-382000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-328000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-557000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-401000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-321000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-205000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-328000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-303000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-319000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-224000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-336000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-311000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-274000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-202000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-347000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-330000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9908,8 +10131,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10030,130 +10256,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-260000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-501000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-577000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9344000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1810000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-533000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-418000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-520000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-422000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-378000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-595000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-591000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-411000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-304000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-194000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-406000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-399000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-310000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-286000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>485000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1368000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-477000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>758000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1092000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1272000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-288000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-506000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-405000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-327000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-131000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-292000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-308000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-244000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-236000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-369000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-276000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-505000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-291000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-309000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-118000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10196,130 +10428,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>672000</v>
+      </c>
+      <c r="E96" s="3">
         <v>674000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>673000</v>
       </c>
       <c r="F96" s="3">
         <v>673000</v>
       </c>
       <c r="G96" s="3">
-        <v>645000</v>
+        <v>673000</v>
       </c>
       <c r="H96" s="3">
         <v>645000</v>
       </c>
       <c r="I96" s="3">
+        <v>645000</v>
+      </c>
+      <c r="J96" s="3">
         <v>650000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>654000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>629000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>633000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>632000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>642000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>624000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>633000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-643000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-666000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-524000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-537000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-551000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-563000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-430000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-440000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-452000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-416000</v>
       </c>
       <c r="AA96" s="3">
         <v>-416000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-416000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-420000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-423000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-428000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-382000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-385000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-387000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-390000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-338000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-340000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-341000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-344000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-299000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-304000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-306000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-309000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10440,8 +10676,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10562,8 +10801,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10684,130 +10926,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1013000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3045000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-629000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4418000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-615000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1553000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2003000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1868000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1608000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1568000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-802000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2757000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2907000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-200000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2117000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>22000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4568000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-386000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5625000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1464000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2907000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2020000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3887000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2033000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-363000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1092000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>243000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2297000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>446000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-203000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1284000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1422000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2215000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>523000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-978000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1547000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1605000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-436000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-1546000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10838,216 +11086,222 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3">
         <v>16000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-32000</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3">
         <v>16000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-32000</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-11000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-3000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>7000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>6000</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>19000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>2000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>3000</v>
-      </c>
-      <c r="AM101" s="3">
-        <v>6000</v>
       </c>
       <c r="AN101" s="3">
         <v>6000</v>
       </c>
       <c r="AO101" s="3">
-        <v>-5000</v>
+        <v>6000</v>
       </c>
       <c r="AP101" s="3">
         <v>-5000</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>-5000</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2386000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-196000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>361000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4239000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1806000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1293000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1510000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1089000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1123000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2316000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-289000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2284000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>544000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1602000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1844000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1710000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1932000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2281000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4988000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1286000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1857000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2002000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3559000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3392000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5686000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>5239000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-78000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1002000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1177000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2462000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1103000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-583000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>686000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>977000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-155000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-953000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-267000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1405000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-402000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-1028000</v>
       </c>
     </row>
